--- a/Boston_Beer_Margin_Comparison.xlsx
+++ b/Boston_Beer_Margin_Comparison.xlsx
@@ -3,7 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
